--- a/src/attributions/attributions_saliency_traj_176.xlsx
+++ b/src/attributions/attributions_saliency_traj_176.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1139 +999,8536 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.455909675016301e-06</v>
+        <v>0.01756485551595688</v>
       </c>
       <c r="B2" t="n">
-        <v>9.205042260873597e-06</v>
+        <v>0.1725072860717773</v>
       </c>
       <c r="C2" t="n">
-        <v>4.230657395964954e-06</v>
+        <v>0.1913023442029953</v>
       </c>
       <c r="D2" t="n">
-        <v>1.755677112669218e-05</v>
+        <v>0.2972620129585266</v>
       </c>
       <c r="E2" t="n">
-        <v>5.044951194577152e-06</v>
+        <v>0.1526902616024017</v>
       </c>
       <c r="F2" t="n">
-        <v>3.301192464277847e-06</v>
+        <v>0.03171689063310623</v>
       </c>
       <c r="G2" t="n">
-        <v>3.318652943562483e-06</v>
+        <v>0.006407702341675758</v>
       </c>
       <c r="H2" t="n">
-        <v>7.318550387935829e-07</v>
+        <v>0.07577104121446609</v>
       </c>
       <c r="I2" t="n">
-        <v>9.850509741227143e-09</v>
+        <v>0.02044143527746201</v>
       </c>
       <c r="J2" t="n">
-        <v>6.186631253513042e-06</v>
+        <v>0.0006914138793945312</v>
       </c>
       <c r="K2" t="n">
-        <v>9.169313671009149e-06</v>
+        <v>0.1909283399581909</v>
       </c>
       <c r="L2" t="n">
-        <v>3.293581585239735e-06</v>
+        <v>0.1338073164224625</v>
       </c>
       <c r="M2" t="n">
-        <v>1.703796442598104e-05</v>
+        <v>0.2726211845874786</v>
       </c>
       <c r="N2" t="n">
-        <v>6.103691703174263e-07</v>
+        <v>0.2013611346483231</v>
       </c>
       <c r="O2" t="n">
-        <v>9.94392394204624e-06</v>
+        <v>0.03197960555553436</v>
       </c>
       <c r="P2" t="n">
-        <v>2.918900236181798e-06</v>
+        <v>0.05652139708399773</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.010649485688191e-06</v>
+        <v>0.1257750540971756</v>
       </c>
       <c r="R2" t="n">
-        <v>5.806295121146832e-06</v>
+        <v>0.01388430967926979</v>
       </c>
       <c r="S2" t="n">
-        <v>1.788164468052855e-06</v>
+        <v>0.02845578268170357</v>
       </c>
       <c r="T2" t="n">
-        <v>3.575190930860117e-06</v>
+        <v>0.06852372735738754</v>
       </c>
       <c r="U2" t="n">
-        <v>6.538504067066242e-07</v>
+        <v>0.01077434420585632</v>
       </c>
       <c r="V2" t="n">
-        <v>5.241259941612952e-07</v>
+        <v>0.1088424399495125</v>
       </c>
       <c r="W2" t="n">
-        <v>3.610903377193608e-06</v>
+        <v>0.05942082405090332</v>
       </c>
       <c r="X2" t="n">
-        <v>3.855596787616378e-06</v>
+        <v>0.069942407310009</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.321437935075664e-06</v>
+        <v>0.07146259397268295</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.135320068598958e-06</v>
+        <v>0.01732102409005165</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.40971791199263e-08</v>
+        <v>0.1306790411472321</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.678169716498815e-06</v>
+        <v>0.08981190621852875</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.732114353420911e-06</v>
+        <v>0.1114017218351364</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.725566663590143e-07</v>
+        <v>0.07525453716516495</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.875572019751417e-06</v>
+        <v>0.008934197947382927</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.481014785706066e-06</v>
+        <v>0.04467065259814262</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.728783217913588e-06</v>
+        <v>0.02504007704555988</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.750873697252246e-07</v>
+        <v>0.06527011096477509</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.382170350756496e-06</v>
+        <v>0.06284914910793304</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.697339141377597e-06</v>
+        <v>0.05925353243947029</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.086616288783262e-06</v>
+        <v>0.05092149972915649</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.103949090174865e-06</v>
+        <v>0.1137273013591766</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.741173770777095e-08</v>
+        <v>0.0513778030872345</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.785063315968728e-06</v>
+        <v>0.01717176660895348</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.31326686414468e-07</v>
+        <v>0.2107787132263184</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.286210342906998e-07</v>
+        <v>0.01307111140340567</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.99171199205739e-07</v>
+        <v>0.03385071456432343</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.421074764759396e-07</v>
+        <v>0.01057309284806252</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.092115098799695e-06</v>
+        <v>0.05874640494585037</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.304628312936984e-06</v>
+        <v>0.01289530284702778</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.957826270881924e-06</v>
+        <v>0.2308692336082458</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.360157840390457e-07</v>
+        <v>0.0345681756734848</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.013463568408042e-06</v>
+        <v>0.09181804955005646</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.404086444585118e-06</v>
+        <v>0.138340950012207</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.581680291768862e-06</v>
+        <v>0.05183383822441101</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.735320206033066e-06</v>
+        <v>0.05372611805796623</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.109772028939915e-06</v>
+        <v>0.03693214803934097</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.779425014727167e-06</v>
+        <v>0.0705789253115654</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.592063866468379e-07</v>
+        <v>0.04198074340820312</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.447267201612704e-06</v>
+        <v>0.2280257344245911</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.167930915675242e-06</v>
+        <v>0.1486735343933105</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.514524102385622e-06</v>
+        <v>0.1200153157114983</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.722807496662426e-07</v>
+        <v>0.260488361120224</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.431590928608784e-06</v>
+        <v>0.04006578773260117</v>
       </c>
       <c r="BI2" t="n">
-        <v>8.240793363256671e-07</v>
+        <v>0.04241866618394852</v>
       </c>
       <c r="BJ2" t="n">
-        <v>8.444558261544444e-07</v>
+        <v>0.1028479114174843</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.436998329358175e-06</v>
+        <v>0.06358800828456879</v>
       </c>
       <c r="BL2" t="n">
-        <v>7.634957000846043e-06</v>
+        <v>0.007163245230913162</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.750322881998727e-06</v>
+        <v>0.1059987917542458</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.580485549216974e-07</v>
+        <v>0.02169011346995831</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.732041027935338e-06</v>
+        <v>0.1024258136749268</v>
       </c>
       <c r="BP2" t="n">
-        <v>2.279071509292407e-07</v>
+        <v>0.09910397976636887</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.407707016682252e-07</v>
+        <v>0.03024611063301563</v>
       </c>
       <c r="BR2" t="n">
-        <v>1.46752108776127e-06</v>
+        <v>0.08420293033123016</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.705353593541076e-07</v>
+        <v>0.01135655865073204</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.34377501126437e-06</v>
+        <v>0.004346912726759911</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.337422413096647e-06</v>
+        <v>0.04944857209920883</v>
       </c>
       <c r="BV2" t="n">
-        <v>3.463362645561574e-06</v>
+        <v>0.261470228433609</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.771563233887719e-07</v>
+        <v>0.007544966414570808</v>
       </c>
       <c r="BX2" t="n">
-        <v>2.555092351030908e-06</v>
+        <v>0.09548968076705933</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.488684680836741e-06</v>
+        <v>0.000283354427665472</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.230981183653057e-06</v>
+        <v>0.0423492044210434</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.457375103404047e-06</v>
+        <v>0.09635111689567566</v>
       </c>
       <c r="CB2" t="n">
-        <v>8.327323257617536e-07</v>
+        <v>0.03994238749146461</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.291004875587532e-06</v>
+        <v>0.1334718316793442</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.847126208711416e-06</v>
+        <v>0.01363273710012436</v>
       </c>
       <c r="CE2" t="n">
-        <v>5.144679562363308e-07</v>
+        <v>0.0905301421880722</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.175289639832044e-06</v>
+        <v>0.05138225853443146</v>
       </c>
       <c r="CG2" t="n">
-        <v>5.184277142689098e-06</v>
+        <v>0.09961055964231491</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.449140881959465e-06</v>
+        <v>0.02877274341881275</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.167097934740013e-06</v>
+        <v>0.0001018106704577804</v>
       </c>
       <c r="CJ2" t="n">
-        <v>6.758955919394793e-07</v>
+        <v>0.01677833124995232</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.426233779966424e-06</v>
+        <v>0.03087181784212589</v>
       </c>
       <c r="CL2" t="n">
-        <v>8.790408401182503e-07</v>
+        <v>0.008109338581562042</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.294945832341909e-06</v>
+        <v>0.04443840682506561</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.890373025365989e-07</v>
+        <v>0.03696988895535469</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.10516418772022e-06</v>
+        <v>0.01163932867348194</v>
       </c>
       <c r="CP2" t="n">
-        <v>6.122013019194128e-06</v>
+        <v>0.0521027073264122</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.491121111030225e-06</v>
+        <v>0.03138300403952599</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.262801106349798e-06</v>
+        <v>0.03532521054148674</v>
       </c>
       <c r="CS2" t="n">
-        <v>5.890597549296217e-06</v>
+        <v>0.04346966370940208</v>
       </c>
       <c r="CT2" t="n">
-        <v>6.464986199716805e-06</v>
+        <v>0.05419072508811951</v>
       </c>
       <c r="CU2" t="n">
-        <v>4.782070391229354e-06</v>
+        <v>0.05542179569602013</v>
       </c>
       <c r="CV2" t="n">
-        <v>4.34826324635651e-06</v>
+        <v>0.004738140851259232</v>
       </c>
       <c r="CW2" t="n">
-        <v>8.682716838848137e-07</v>
+        <v>0.08716214448213577</v>
       </c>
       <c r="CX2" t="n">
-        <v>2.587231335837714e-07</v>
+        <v>0.04195567592978477</v>
       </c>
       <c r="CY2" t="n">
-        <v>3.992436631961027e-06</v>
+        <v>0.09504073858261108</v>
       </c>
       <c r="CZ2" t="n">
-        <v>9.000235650091781e-07</v>
+        <v>0.005949687678366899</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.974964106921107e-06</v>
+        <v>0.006098866928368807</v>
       </c>
       <c r="DB2" t="n">
-        <v>4.269768396625295e-07</v>
+        <v>0.01273473910987377</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.602152224222664e-06</v>
+        <v>0.03120434656739235</v>
       </c>
       <c r="DD2" t="n">
-        <v>6.517249175885809e-07</v>
+        <v>0.02086749114096165</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.102373971662018e-06</v>
+        <v>0.02793596126139164</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.034006709232926e-05</v>
+        <v>0.234153687953949</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.636474841390736e-06</v>
+        <v>0.1232021972537041</v>
       </c>
       <c r="DH2" t="n">
-        <v>3.575565187929897e-06</v>
+        <v>0.01774477586150169</v>
       </c>
       <c r="DI2" t="n">
-        <v>6.192657565406989e-06</v>
+        <v>0.03503585234284401</v>
       </c>
       <c r="DJ2" t="n">
-        <v>8.242560397775378e-06</v>
+        <v>0.03386125713586807</v>
       </c>
       <c r="DK2" t="n">
-        <v>8.350368261744734e-06</v>
+        <v>0.02821259573101997</v>
       </c>
       <c r="DL2" t="n">
-        <v>1.304898546550248e-06</v>
+        <v>0.004356806632131338</v>
       </c>
       <c r="DM2" t="n">
-        <v>2.258996346427011e-06</v>
+        <v>0.1141309216618538</v>
       </c>
       <c r="DN2" t="n">
-        <v>3.767326688830508e-06</v>
+        <v>0.01482691057026386</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.903560814753291e-06</v>
+        <v>0.01228554546833038</v>
       </c>
       <c r="DP2" t="n">
-        <v>4.937413450534223e-06</v>
+        <v>0.05238775908946991</v>
       </c>
       <c r="DQ2" t="n">
-        <v>7.410770194837824e-06</v>
+        <v>0.04135628789663315</v>
       </c>
       <c r="DR2" t="n">
-        <v>2.237893284018355e-07</v>
+        <v>0.09120699018239975</v>
       </c>
       <c r="DS2" t="n">
-        <v>2.893659711844521e-07</v>
+        <v>0.135717511177063</v>
       </c>
       <c r="DT2" t="n">
-        <v>5.119186425872613e-07</v>
+        <v>0.09974098205566406</v>
       </c>
       <c r="DU2" t="n">
-        <v>2.325170726180659e-06</v>
+        <v>0.1290156096220016</v>
       </c>
       <c r="DV2" t="n">
-        <v>1.231585201821872e-06</v>
+        <v>0.068498395383358</v>
       </c>
       <c r="DW2" t="n">
-        <v>5.408468496170826e-06</v>
+        <v>0.05044259130954742</v>
       </c>
       <c r="DX2" t="n">
-        <v>3.748946710402379e-06</v>
+        <v>0.0144931972026825</v>
       </c>
       <c r="DY2" t="n">
-        <v>2.500181324194273e-07</v>
+        <v>0.06401427835226059</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2.875735162888304e-06</v>
+        <v>0.06506885588169098</v>
       </c>
       <c r="EA2" t="n">
-        <v>1.497568860031606e-06</v>
+        <v>0.2222537249326706</v>
       </c>
       <c r="EB2" t="n">
-        <v>4.595774498739047e-06</v>
+        <v>0.1952198147773743</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.605865120131057e-06</v>
+        <v>0.006705655250698328</v>
       </c>
       <c r="ED2" t="n">
-        <v>4.311170869186753e-06</v>
+        <v>0.1523509174585342</v>
       </c>
       <c r="EE2" t="n">
-        <v>1.980506795007386e-06</v>
+        <v>0.03304822742938995</v>
       </c>
       <c r="EF2" t="n">
-        <v>6.638699119321245e-07</v>
+        <v>0.006303679198026657</v>
       </c>
       <c r="EG2" t="n">
-        <v>5.483608447320876e-07</v>
+        <v>0.0758049413561821</v>
       </c>
       <c r="EH2" t="n">
-        <v>2.189221959270071e-07</v>
+        <v>0.02304054982960224</v>
       </c>
       <c r="EI2" t="n">
-        <v>8.719311153981835e-06</v>
+        <v>0.1840080916881561</v>
       </c>
       <c r="EJ2" t="n">
-        <v>1.561034082442347e-06</v>
+        <v>0.00266578933224082</v>
       </c>
       <c r="EK2" t="n">
-        <v>1.088003045879304e-06</v>
+        <v>0.04460791125893593</v>
       </c>
       <c r="EL2" t="n">
-        <v>4.906456751996302e-08</v>
+        <v>0.012293366715312</v>
       </c>
       <c r="EM2" t="n">
-        <v>4.11404244005098e-06</v>
+        <v>0.01803196035325527</v>
       </c>
       <c r="EN2" t="n">
-        <v>1.550146180306911e-06</v>
+        <v>0.01383988372981548</v>
       </c>
       <c r="EO2" t="n">
-        <v>6.550527359650005e-06</v>
+        <v>0.0003933787811547518</v>
       </c>
       <c r="EP2" t="n">
-        <v>3.246510686949478e-07</v>
+        <v>0.08228326588869095</v>
       </c>
       <c r="EQ2" t="n">
-        <v>4.134831669944106e-06</v>
+        <v>0.02509825862944126</v>
       </c>
       <c r="ER2" t="n">
-        <v>3.578722726160777e-06</v>
+        <v>0.01608037762343884</v>
       </c>
       <c r="ES2" t="n">
-        <v>9.215174259225023e-07</v>
+        <v>7.227109745144844e-05</v>
       </c>
       <c r="ET2" t="n">
-        <v>5.424971277534496e-06</v>
+        <v>0.0112285390496254</v>
       </c>
       <c r="EU2" t="n">
-        <v>1.450876197850448e-06</v>
+        <v>0.01230919919908047</v>
       </c>
       <c r="EV2" t="n">
-        <v>1.062828346221067e-06</v>
+        <v>0.007947632111608982</v>
       </c>
       <c r="EW2" t="n">
-        <v>1.782460685717524e-06</v>
+        <v>0.0234735868871212</v>
       </c>
       <c r="EX2" t="n">
-        <v>5.237563982518623e-06</v>
+        <v>0.01550829783082008</v>
       </c>
       <c r="EY2" t="n">
-        <v>1.184384814223449e-06</v>
+        <v>0.1091547906398773</v>
       </c>
       <c r="EZ2" t="n">
-        <v>3.61653576419485e-07</v>
+        <v>0.04503615573048592</v>
       </c>
       <c r="FA2" t="n">
-        <v>5.19750847161049e-06</v>
+        <v>0.08210116624832153</v>
       </c>
       <c r="FB2" t="n">
-        <v>1.462932800677663e-06</v>
+        <v>0.005404634866863489</v>
       </c>
       <c r="FC2" t="n">
-        <v>1.029273221320182e-06</v>
+        <v>0.02953390218317509</v>
       </c>
       <c r="FD2" t="n">
-        <v>3.383596549610957e-07</v>
+        <v>0.01222243066877127</v>
       </c>
       <c r="FE2" t="n">
-        <v>8.140576710502501e-07</v>
+        <v>0.0269598513841629</v>
       </c>
       <c r="FF2" t="n">
-        <v>1.854866809480882e-06</v>
+        <v>0.01554816775023937</v>
       </c>
       <c r="FG2" t="n">
-        <v>2.589453288237564e-06</v>
+        <v>0.01813435554504395</v>
       </c>
       <c r="FH2" t="n">
-        <v>5.964837328065187e-06</v>
+        <v>0.1176333427429199</v>
       </c>
       <c r="FI2" t="n">
-        <v>1.571892653373652e-06</v>
+        <v>0.08923614025115967</v>
       </c>
       <c r="FJ2" t="n">
-        <v>3.651229235401843e-06</v>
+        <v>0.07357347011566162</v>
       </c>
       <c r="FK2" t="n">
-        <v>4.337920472607948e-06</v>
+        <v>0.04090851917862892</v>
       </c>
       <c r="FL2" t="n">
-        <v>9.420044762009638e-07</v>
+        <v>0.06917913258075714</v>
       </c>
       <c r="FM2" t="n">
-        <v>2.854961167031433e-06</v>
+        <v>0.07395081222057343</v>
       </c>
       <c r="FN2" t="n">
-        <v>1.73725277363701e-06</v>
+        <v>0.2205543220043182</v>
       </c>
       <c r="FO2" t="n">
-        <v>9.754629672897863e-07</v>
+        <v>0.1252936273813248</v>
       </c>
       <c r="FP2" t="n">
-        <v>9.350585969514214e-06</v>
+        <v>0.105598121881485</v>
       </c>
       <c r="FQ2" t="n">
-        <v>4.711398105428088e-06</v>
+        <v>0.003590492531657219</v>
       </c>
       <c r="FR2" t="n">
-        <v>1.660178213569452e-06</v>
+        <v>0.174371674656868</v>
       </c>
       <c r="FS2" t="n">
-        <v>7.997701345630048e-07</v>
+        <v>0.1591237187385559</v>
       </c>
       <c r="FT2" t="n">
-        <v>4.265496045263717e-08</v>
+        <v>0.1553504467010498</v>
       </c>
       <c r="FU2" t="n">
-        <v>2.602544100227533e-06</v>
+        <v>0.1211569383740425</v>
       </c>
       <c r="FV2" t="n">
-        <v>1.230737871082965e-05</v>
+        <v>0.001699227839708328</v>
       </c>
       <c r="FW2" t="n">
-        <v>7.731640835118014e-06</v>
+        <v>0.06261239945888519</v>
       </c>
       <c r="FX2" t="n">
-        <v>1.191286060020502e-06</v>
+        <v>0.02448766306042671</v>
       </c>
       <c r="FY2" t="n">
-        <v>1.063293166225776e-05</v>
+        <v>0.02183706685900688</v>
       </c>
       <c r="FZ2" t="n">
-        <v>1.167537789115158e-06</v>
+        <v>0.08001388609409332</v>
       </c>
       <c r="GA2" t="n">
-        <v>9.162807145912666e-06</v>
+        <v>0.0226963646709919</v>
       </c>
       <c r="GB2" t="n">
-        <v>3.14813814838999e-06</v>
+        <v>0.01909055560827255</v>
       </c>
       <c r="GC2" t="n">
-        <v>4.080553026142297e-06</v>
+        <v>0.07053621113300323</v>
       </c>
       <c r="GD2" t="n">
-        <v>5.84699000683031e-06</v>
+        <v>0.06410022079944611</v>
       </c>
       <c r="GE2" t="n">
-        <v>4.0700124372961e-06</v>
+        <v>0.06527668237686157</v>
       </c>
       <c r="GF2" t="n">
-        <v>4.487087153393077e-06</v>
+        <v>0.00826294906437397</v>
       </c>
       <c r="GG2" t="n">
-        <v>3.321365966257872e-06</v>
+        <v>0.03931739553809166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.007653671316802502</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.002093638526275754</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.001911025959998369</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.002519611269235611</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.003361999755725265</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.001425487571395934</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.004432028159499168</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.002683197148144245</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.002677866723388433</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.009048890322446823</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.002692607697099447</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.002887086244300008</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.001844780053943396</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.48398238606751e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.001288517960347235</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.006474790163338184</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.002210281090810895</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.005292642395943403</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>8.99308652151376e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.0003360059927217662</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.0009820640552788973</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8.000506204552948e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.001629574806429446</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.002340527484193444</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.0003515192365739495</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.000332256022375077</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.0001399737957399338</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.0001211320050060749</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.001451795920729637</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.0001038542250171304</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.0002284785732626915</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.00366720394231379</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.00227234442718327</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.0002014100318774581</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.0007689954363740981</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.0002376808552071452</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.001596910762600601</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.001107458956539631</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.001070216880179942</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.0001233939256053418</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.0004053000593557954</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.000481027236673981</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.0005007801228202879</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.0002020420215558261</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.0005477478844113648</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.005984452553093433</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.001047978410497308</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.0006047493661753833</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.0006891884258948267</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.002437087241560221</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.0005306859966367483</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.002900988794863224</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.00195968896150589</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.0006354082725010812</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.001877470873296261</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.002014387864619493</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.001028898055665195</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.0006758481031283736</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.0005489416653290391</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.0005853681359440088</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0001385334180667996</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.002220474882051349</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.001548165222629905</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.001100497785955667</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>8.778710616752505e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.0006310916505753994</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.001014744630083442</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.0008923158748075366</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.0002254122955491766</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.0006035068654455245</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.000620824983343482</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.0007693814113736153</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.003379122354090214</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.0004184255958534777</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.002281212713569403</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.000815514475107193</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.001985537121072412</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.0006777152884751558</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.001345191383734345</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.0003098355373367667</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.0009458588319830596</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.002597301732748747</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.001165057765319943</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.0002812923339661211</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.0007875573355704546</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.0009233016753569245</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.000662459060549736</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.001152530778199434</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>0.0003330419422127306</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.0002799434878397733</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.00102663692086935</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.004544546827673912</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.002770077437162399</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.001553633948788047</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.002411006484180689</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.003494789358228445</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.002077027224004269</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.001318604568950832</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>8.136135147651657e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.002387666143476963</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.001147447037510574</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.0003341895644553006</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.0009045263286679983</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.001521259895525873</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.000951037451159209</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.001365789212286472</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>6.058273720555007e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.0004288294294383377</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>3.434788959566504e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.002685559447854757</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.0008170298533514142</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.001051549217663705</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.004435074515640736</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.0003396036045160145</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.001127570634707808</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.0005539371632039547</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.0006443652091547847</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.0009504682384431362</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.0007055891328491271</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.000175516412127763</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.0004125646082684398</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.000266103888861835</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.0009138796012848616</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.0009708746802061796</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.001220407779328525</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.001810511574149132</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>2.372520975768566e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.002262675669044256</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.0003788752947002649</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>7.346348138526082e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.001869457424618304</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.002651954302564263</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.002641443628817797</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.002182723954319954</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.001190975657664239</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.001956155290827155</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.001069205580279231</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.0006242440431378782</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.002499321242794394</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>7.779795851092786e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>8.100876584649086e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.0009209983400069177</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.0006315823993645608</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>1.129077281802893e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.001889154664240777</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.0009780068648979068</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.001181296305730939</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.0006731795729137957</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.002655881689861417</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.0004312264791224152</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.001133695943281054</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.0007043547811917961</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.001269247615709901</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.003005892736837268</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.001754643628373742</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>9.820342529565096e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.0007973727188073099</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.001209917012602091</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.0001440085179638118</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.001459991093724966</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.0002770120627246797</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.0001273609377676621</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.002728541381657124</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.0002902273554354906</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.001068669138476253</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.001225891872309148</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.0008768438128754497</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.0002124878374161199</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.001223929924890399</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.0008562038419768214</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.0008245576755143702</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.003635917324572802</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.0007731935475021601</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.003408747958019376</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.002096070675179362</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.003351202700287104</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.002498433459550142</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.002011624164879322</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.0009462033631280065</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.002641757717356086</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.001398852095007896</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.000883660395629704</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.0004864088259637356</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.0008788150153122842</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.0008620474254712462</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.004974791314452887</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.002149453852325678</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.0008363505476154387</v>
       </c>
       <c r="GG3" t="n">
+        <v>0.001155515783466399</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.3936551809310913</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1.317413210868835</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03688104450702667</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1661745756864548</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6554940938949585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.472342133522034</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2648102045059204</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2009989619255066</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1901126354932785</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2660247087478638</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.431643009185791</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1111671775579453</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.139972060918808</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0468992292881012</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.191563606262207</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1332127302885056</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2196642607450485</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1950755715370178</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1862323433160782</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2997133433818817</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4827683568000793</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.2438198179006577</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.23496975004673</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1492268443107605</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5970227718353271</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2123578041791916</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.1903756111860275</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3453453779220581</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3961447775363922</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1520460247993469</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.7900543808937073</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.258118599653244</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.4887420237064362</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2894081473350525</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.5819153189659119</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4041711986064911</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.1279842406511307</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1431975662708282</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.08717351406812668</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.159906804561615</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.2402570098638535</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.348182201385498</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.3720683157444</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.2977831959724426</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.002395575866103172</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.2011866569519043</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.7447627782821655</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.3570233285427094</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1550136208534241</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.6159095764160156</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.9567838311195374</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.3546690046787262</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.03455165401101112</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.3060207962989807</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.1666984111070633</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.7096754312515259</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.1860943287611008</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.4824550747871399</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.6875342130661011</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.5194953680038452</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.03951486945152283</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.2685497105121613</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.05519179627299309</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.165322944521904</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.1931100636720657</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.0801365002989769</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.1363435238599777</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.1410947889089584</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.279651403427124</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.08005101978778839</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.1484156399965286</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.1998934894800186</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.1691932678222656</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2820922434329987</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.3920820951461792</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.1564759612083435</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.2629460096359253</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.6078653335571289</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.6907001137733459</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.06347960233688354</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.05316229909658432</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.02741389349102974</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.3914156556129456</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.05875001475214958</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.1255318522453308</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.1640141606330872</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.2964420914649963</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.03257013484835625</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.04579995200037956</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.03253427147865295</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.4373945593833923</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.6642548441886902</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0.5826042890548706</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.3512342572212219</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.04603758454322815</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.4002283215522766</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.09624569863080978</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.2971701622009277</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.2754559516906738</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.008090440183877945</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.3650079965591431</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.02997633069753647</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.07459539175033569</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.1561486721038818</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.2587148547172546</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.06754808872938156</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.003212458454072475</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.01281291805207729</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.5998398661613464</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.1398004293441772</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.4574080109596252</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.1355636417865753</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.1545234769582748</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>1.20527708530426</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0.2285926043987274</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.3559769690036774</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0.3576263189315796</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.04039386659860611</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.3277939260005951</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0.1817936152219772</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.2120799124240875</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.02570826932787895</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.01419054344296455</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.07687074691057205</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0.0731954351067543</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0.1197942867875099</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.1829337179660797</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.2943467497825623</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0.02257886528968811</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.1293379068374634</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.3500159680843353</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.4559561312198639</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.06087155267596245</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0.6668632030487061</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0.5705752372741699</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0.1151104420423508</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.09324456751346588</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0.2157622277736664</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.5207058787345886</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.1901426911354065</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.2520280480384827</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.1259453594684601</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.2019454389810562</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.1315497159957886</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.03503571450710297</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.2320939898490906</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0.36414435505867</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.3072038292884827</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.5354918837547302</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.4623698890209198</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0.09198924899101257</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0.2477521747350693</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0.1158382892608643</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0.01400761306285858</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.3479258418083191</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0.02938777394592762</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.05387171357870102</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.2394163310527802</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.2795807719230652</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0.01342107355594635</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0.006095591932535172</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0.07489396631717682</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0.2698087096214294</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.008117590099573135</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0.324173629283905</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.0621422603726387</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.2939814627170563</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.5975984930992126</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0.190192848443985</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0.1191890314221382</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0.7487644553184509</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0.7880424857139587</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.2131998240947723</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0.2552335262298584</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.1013582646846771</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.02255983650684357</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.1716598868370056</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0.3897309303283691</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0.3114146292209625</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0.1368381679058075</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0.2584978938102722</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.03124254941940308</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0.1455226838588715</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.01709392294287682</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>0.7696675658226013</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.3045052886009216</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0.1616593152284622</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0.2478416115045547</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0.3746767342090607</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.1687134951353073</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5825459957122803</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1090858429670334</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01460480690002441</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1358888894319534</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6591134667396545</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1150708720088005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1869998127222061</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1086196526885033</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.09275083988904953</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7319374680519104</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1313859820365906</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1232918053865433</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3441819548606873</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6870163679122925</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1126964390277863</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02194499224424362</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1164831221103668</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.021673783659935</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.07778312265872955</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1063172221183777</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2469829767942429</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2052392512559891</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1406280547380447</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.006403055042028427</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1150194332003593</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.08908636868000031</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.03912384808063507</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1282613575458527</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.07283299416303635</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1464322805404663</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.2917347252368927</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.05379799380898476</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.04172033444046974</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3720863163471222</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.0469885878264904</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.01914717443287373</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1640596389770508</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.09337042272090912</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.1450366973876953</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.08835896104574203</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.03289197757840157</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.06559692323207855</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.14662966132164</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.1759616285562515</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.08071266859769821</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.7076403498649597</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.1217696964740753</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.06515099108219147</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.2171145677566528</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.320089727640152</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.06257498264312744</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.01125319674611092</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.1282387524843216</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.008046945556998253</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.08447498828172684</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.1084711104631424</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.003238491714000702</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.04075039178133011</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.0239180400967598</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.1054493486881256</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.1162516176700592</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.01166456937789917</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.05323365703225136</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.09797336161136627</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.002097122371196747</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.1338584870100021</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.05832165479660034</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.07625214010477066</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.322172224521637</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.03249362111091614</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.1085636913776398</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.004665158689022064</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.4179526567459106</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.08034424483776093</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.2419417947530746</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.1370286047458649</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.2777639329433441</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.06589552760124207</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.003896888345479965</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.1169047206640244</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.03226824104785919</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.2105109393596649</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.003132140263915062</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.07149146497249603</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.001752523705363274</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1618320941925049</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.1068270280957222</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.04829566180706024</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.04701566696166992</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.1310074925422668</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.3152124285697937</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.135967418551445</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.1661963313817978</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.09437482804059982</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.01336546335369349</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.1004156470298767</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.05394625663757324</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.0008134488016366959</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.003901451826095581</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.1804750114679337</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.01069285161793232</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.04534278810024261</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.02358058281242847</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.1738979816436768</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.08303894102573395</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.04698636382818222</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.04344042763113976</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.08289715647697449</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.06495872884988785</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.1232920438051224</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.004968859255313873</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.1369132399559021</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.07797777652740479</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0.05850427597761154</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.1231486648321152</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0.006698757410049438</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.03086556307971478</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.1145462021231651</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.02522116340696812</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.05200110003352165</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.07459516823291779</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.07024006545543671</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.05006223544478416</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.1285486370325089</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0.06000664830207825</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.06296905130147934</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.04613641649484634</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.07612656056880951</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0.09123882651329041</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.09808658063411713</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.2165394276380539</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.02419654838740826</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.07330885529518127</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.1203963160514832</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0.01017807144671679</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.02053478732705116</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.05143387988209724</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.2691252529621124</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0.04585538804531097</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.1113447248935699</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0.03296181559562683</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0.01499606110155582</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.0629105344414711</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0.0111885666847229</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.0939665287733078</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.0284455306828022</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.00751453684642911</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.05284766852855682</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.03193987160921097</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0.04078233987092972</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0.003760357387363911</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0.03293333202600479</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0.02421843446791172</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.2177609354257584</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.00900283083319664</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.05264934152364731</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.008195577189326286</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1649788022041321</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.1130454316735268</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.06205397099256516</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.0003059064038097858</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.01590249314904213</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.1923507153987885</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.09878087788820267</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.03509954363107681</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.06366819143295288</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.201333612203598</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0.1151371151208878</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.3389222323894501</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.1017254889011383</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.1235402002930641</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.206306129693985</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.1590757668018341</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.2160577774047852</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.05400527268648148</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.2806412875652313</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.161776602268219</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.2327374964952469</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0.1496747881174088</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0.08351270854473114</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.00904412753880024</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.09657615423202515</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0.06947418302297592</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.2072499841451645</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.1742905974388123</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0.04652439802885056</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0.0925496444106102</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0.1046570837497711</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.8814365267753601</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.079211235046387</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08232110738754272</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1265913248062134</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.009818203747272491</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8684563636779785</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.237181156873703</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3700259625911713</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3579142987728119</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8658869862556458</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.368801593780518</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1219508200883865</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.09445834159851074</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4379483461380005</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7958148717880249</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2623133957386017</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.03868499025702477</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6466156244277954</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.04559818655252457</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1525321006774902</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2172373831272125</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.3552015721797943</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2475364953279495</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1984752118587494</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.03335501626133919</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.3881382644176483</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2121957391500473</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2676438987255096</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.2592365741729736</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.135719433426857</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.4009090960025787</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.6127981543540955</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.2300230115652084</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.04022384807467461</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3539484143257141</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.135283350944519</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.279105931520462</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3368066549301147</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.2462557256221771</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.3137500882148743</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.2054810523986816</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.0584726445376873</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.1945604085922241</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.2999059557914734</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.2924199402332306</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.5976205468177795</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.9211850166320801</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.1495977342128754</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.08085452765226364</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.3365451097488403</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.2678846418857574</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.03912116959691048</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.005179326981306076</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.2443539947271347</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.0970127210021019</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.1540862917900085</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.1628105044364929</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.1258554011583328</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.01291875913739204</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.393677294254303</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.007082387804985046</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.1069314256310463</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.2256947159767151</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.04391765594482422</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.01860745996236801</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.01489480584859848</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.1765262931585312</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.006568446755409241</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.07932888716459274</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.5863379836082458</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.1477949023246765</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.1864243596792221</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.2124472856521606</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.6298642754554749</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.1597100496292114</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.3064318597316742</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.1263595670461655</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.3908550441265106</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.01231859996914864</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.09446442127227783</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.236614465713501</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.1421501338481903</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.3690476417541504</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.05513139814138412</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.0568956583738327</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.07503394037485123</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.2569038867950439</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.2208354473114014</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.1014277711510658</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.07206293940544128</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.03196738660335541</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.600270688533783</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.1036003232002258</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.4167217016220093</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.1249480694532394</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.3003665804862976</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.09934291988611221</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.02140634320676327</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.01062953658401966</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.1090573072433472</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.3363300859928131</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.076442651450634</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.04218724370002747</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.0516449399292469</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.2487879395484924</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.1613814830780029</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.1598956882953644</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.08890770375728607</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.09324023872613907</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.08437118679285049</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.194225400686264</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.08528220653533936</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.6772214770317078</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.1804017424583435</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.03798851370811462</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.1166285425424576</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.3399231135845184</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.07251125574111938</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.2412870675325394</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.1532424092292786</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.01580528914928436</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.07871781289577484</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.4576001465320587</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.1357402503490448</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.4369379878044128</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0.107372872531414</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.1782139539718628</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.0497349314391613</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.05015353858470917</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.2782585620880127</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.4783340990543365</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.4713797569274902</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.07439962774515152</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.0371897853910923</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0.1899380832910538</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0.1641715317964554</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.01664992235600948</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0.1939169764518738</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.4126361012458801</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.08287882059812546</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.1425317078828812</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.1347109377384186</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.08070756494998932</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.09541371464729309</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.09891974925994873</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.1086784899234772</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0.08199108392000198</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.09861301630735397</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.07385167479515076</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.2831905782222748</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0.04389848187565804</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0.09721500426530838</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0.3308188319206238</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0.1453593224287033</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.4107268452644348</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0.03835196048021317</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.03715546429157257</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.09799767285585403</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.2350378632545471</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0.1963851600885391</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0.1737905889749527</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0.02235441654920578</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0.002513822168111801</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.5089389085769653</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0.2011306285858154</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.03787905722856522</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.1622849106788635</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.3657507598400116</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0.1677137613296509</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0.6590055227279663</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0.003222904168069363</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0.3137540221214294</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.3344619572162628</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.6987802982330322</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.5102362632751465</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.123960979282856</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.3429750204086304</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0.2585241794586182</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.03453517705202103</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.1391442716121674</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.181998610496521</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.1892645061016083</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.1028450727462769</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.2162919938564301</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.3301198780536652</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.2113535553216934</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.04609478265047073</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.3020032346248627</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.4217050075531006</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.002022115048021078</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00316874566487968</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9.074353147298098e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0002329037815798074</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0001122546382248402</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0009876481490209699</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0002740579366218299</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.76876671705395e-05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0004488354607019573</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001738610561005771</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.003117634681984782</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.830661833286285e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001822206395445392</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0009020054712891579</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001312708482146263</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0002782439114525914</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0002357519988436252</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.001311213010922074</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0001567452272865921</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0001864177174866199</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.000646707194391638</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0002648858062457293</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0006406131433323026</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0004583889967761934</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0003307395672891289</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.000573899014852941</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0002912705531343818</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0001649563491810113</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.0004706631298176944</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.701141784200445e-05</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.001199442427605391</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.001011243322864175</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0002741670468822122</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0003902701428160071</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0003518653102219105</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.0002218809968326241</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0006521038594655693</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0004165962163824588</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0005548863555304706</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.0008382954983972013</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.0001906899851746857</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0003739822132047266</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.0004549346631392837</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.684775219880976e-05</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.000283284520264715</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.001141004380770028</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.001536114141345024</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.697241820394993e-05</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.0001755320554366335</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.0004718094714917243</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.0005915459478273988</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.136184386676177e-05</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.0003747001173906028</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.00048481734120287</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0006573583232238889</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.00111160718370229</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0006668792921118438</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.0003430490614846349</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.0004680515849031508</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.0006945634377188981</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.0004322150489315391</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0001059915157384239</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.000193640953511931</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.0003429072094149888</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>3.147528332192451e-05</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.0001101391389966011</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>8.97036079550162e-05</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0005663505289703608</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.0001204745058203116</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0004299305728636682</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.0001108327851397917</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0006090586539357901</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.001257933094166219</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.001040803617797792</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0003464178298600018</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>3.922734322259203e-05</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0001696722465567291</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.000955048599280417</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0003022262535523623</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>4.179793177172542e-05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.0004546134732663631</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.0007568206638097763</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0009261876693926752</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.0002396957424934953</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.0001270896173082292</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0001675223174970597</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.0003473151300568134</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.0002107121399603784</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>2.123067315551452e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.000158181122969836</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0002445210702717304</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.0009650532156229019</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0006123937200754881</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0002431124594295397</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.001058508642017841</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.001006115227937698</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.00018554792040959</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.0001210074624395929</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0001736556005198509</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.0006891221855767071</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.0008601074805483222</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.0002494755899533629</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>1.164684363175184e-05</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>6.879600550746545e-05</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0003585811064112931</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>4.578192238113843e-05</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.0003078912559431046</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>8.700244507053867e-05</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0002411031455267221</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0005200939485803246</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.0001259567943634465</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.000109617249108851</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.001455101883038878</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>5.10932004544884e-05</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0002390354638919234</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.0004521754162851721</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.0002938054676633328</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0002456335350871086</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.0006703899707645178</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.0003459531581029296</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0001406023366143927</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.0004440069023985416</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0007617360097356141</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.0001189401300507598</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.0008205560734495521</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.000513301813043654</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0002911564079113305</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0002961969003081322</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>2.726742241065949e-05</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0004167909501120448</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.000407684245146811</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.0002628407382871956</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.0003151503915432841</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0007382447365671396</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0004122049431316555</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.0006831163773313165</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.0001128120929934084</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.0004317625134717673</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>1.613048152648844e-05</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>6.841150752734393e-05</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0001670228084549308</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>2.331315772607923e-05</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.0001211129856528714</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>9.983289055526257e-05</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.000856796046718955</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.0003470747615210712</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.0004915278404951096</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.0003097292792517692</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.0006701034144498408</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0007753329118713737</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.0001427139359293506</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>1.751731906551868e-05</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0007180021493695676</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0008334058802574873</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.000944664585404098</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0.0001387683878419921</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>3.176328027620912e-05</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.0003305693971924484</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.0002637183351907879</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.000192134320968762</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.0001478893245803192</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>1.402110501658171e-05</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0.0002076491655316204</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.0007818789454177022</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.000264536589384079</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.0002892579068429768</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>5.298420001054183e-05</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.0008781231008470058</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>9.005684842122719e-05</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.0004063656087964773</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.0003970995894633234</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.0007741062436252832</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.00122011941857636</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.0003454737307038158</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.0008341344073414803</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.0004223725118208677</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.00070334249176085</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.0006347484304569662</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.000897525402251631</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.0005101852584630251</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.0008036953513510525</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>2.050771581707522e-05</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.0003682919195853174</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.0004673442163038999</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>1.130733289755881e-05</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.0005325438687577844</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.000446546240709722</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>1.32914719870314e-05</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.0008901820983737707</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.000639759935438633</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.008497780188918114</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.003225820604711771</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0007193464552983642</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.003068368881940842</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.002669706707820296</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00371658755466342</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.002771692350506783</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.862075391225517e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0005411626771092415</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.008401242084801197</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8.974154479801655e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.371251169592142e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.007723216433078051</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0002634010743349791</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.003112014150246978</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.001045252196490765</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.001420245505869389</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.000734523928258568</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.003351898398250341</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.0006086248904466629</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.002381957834586501</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.002448592334985733</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.001070064725354314</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.0003473898686934263</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.001889097969979048</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.811474354937673e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.632191171869636e-05</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.002652494236826897</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.000907098117750138</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.002570019103586674</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.002497881185263395</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.003275791648775339</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.001702383044175804</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.003380011534318328</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.0004224704462103546</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.001735610887408257</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.001123489113524556</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4.540011286735535e-05</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.0009773754281923175</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.005300410091876984</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.001213344745337963</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.001045504352077842</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.005339765921235085</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.000396775285480544</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.001045489101670682</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.00919062178581953</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.000144974168506451</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.001162846339866519</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.004293325822800398</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.004529931582510471</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.001702128327451646</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.001346667762845755</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.002692059148102999</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.00186812283936888</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.0102753471583128</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.003043809905648232</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.0005380198126658797</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.01119550503790379</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.002632124116644263</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.003869282547384501</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.005348253529518843</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.001460715895518661</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.001305280835367739</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.001361463451758027</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.002194510772824287</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.001086077769286931</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.003690841142088175</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.0009969000238925219</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.0003646198892965913</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.003808173816651106</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.001709745032712817</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.0006462409510277212</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.01190176699310541</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.0007990298327058554</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.005605659913271666</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.003367445431649685</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>9.006870095618069e-05</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.001746521447785199</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.0003842188161797822</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.0009378213435411453</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.0002517080283723772</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.003487418871372938</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.001636231900192797</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.0003739297389984131</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.000116318988148123</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.0009112565312534571</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>2.903881249949336e-05</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.0008422674145549536</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.0004806470824405551</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.001658950699493289</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.0005413804901763797</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.0005302127101458609</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.006113122683018446</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.005274786613881588</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.002779850969091058</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.001148468698374927</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.006458839401602745</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.001417238730937243</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.0006853777449578047</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.003056869842112064</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.001298200455494225</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>6.618426414206624e-05</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.001108788652345538</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.0007468011463060975</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.0002752047730609775</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.0002338477352168411</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.0001751703675836325</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.002748613012954593</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.00418563699349761</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.001558745745569468</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.005660783965140581</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.008663024753332138</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.002620380371809006</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.0003758019302040339</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.0002057100064121187</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.002220621798187494</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.00121092249173671</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.003234173404052854</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.001456455327570438</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.0001514634641353041</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.001842587953433394</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.0003620826173573732</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.0007234456134028733</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.0006200007046572864</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.003660125192254782</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.002129733562469482</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.00074995361501351</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.002203633543103933</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.005221971310675144</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.003176273312419653</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.0002464193385094404</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.0008358104387298226</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.003119642846286297</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.004603514913469553</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.0002525594318285584</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.001726481830701232</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.0004150893073529005</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.001203275984153152</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.003002437297254801</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.001125775626860559</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.0009368091123178601</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.0008306492236442864</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>6.243295501917601e-06</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.002220427617430687</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.001915812026709318</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.0005389467696659267</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.002046414650976658</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.001545125851407647</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.00350986747071147</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.001437009195797145</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.003457727609202266</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.003599818795919418</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>5.055704968981445e-05</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.003788629313930869</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.001368471886962652</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.0004564701521303505</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.0001284018362639472</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.0007069921121001244</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>3.952969564124942e-06</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.0005560137215070426</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>7.673125946894288e-05</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.0009999055182561278</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.00318989297375083</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.0001180701947305351</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.002473814180120826</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.0001346632489003241</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.0001663577859289944</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.0002337027690373361</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.002165540121495724</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.002108077518641949</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.000622566556558013</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.006135543808341026</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.01051237620413303</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.0001720073341857642</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.005468974355608225</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.004321866203099489</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.003479841630905867</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.004614759236574173</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.008526780642569065</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.002968429354950786</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.003004401456564665</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.0002464347053319216</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>2.023961860686541e-05</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.001477048732340336</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.0005002492107450962</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.0008505895384587348</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.003679258748888969</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.001841131597757339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3.130992354272166e-08</v>
+      </c>
+      <c r="B12" t="n">
+        <v>9.067500172932341e-08</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.581697439689833e-08</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.438044433006326e-09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.278525184668979e-08</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.127724485490035e-08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.046164375244189e-09</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.544111220639024e-08</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.42972735264857e-08</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.24187529546316e-09</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.225545958050134e-07</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.942587139566967e-08</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6.966028109900435e-08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.01522115159014e-08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.431827515029909e-09</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.457018114109815e-09</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.008648784610159e-08</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.820860428049855e-08</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.054216790587816e-08</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5.109534129132953e-08</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.156871303782282e-08</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.778359929957787e-09</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.058508303231065e-08</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.029167411876642e-08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.341070335480481e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.135223719003989e-08</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.98127519630043e-09</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.237128799402853e-08</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.963744887869325e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.405806043270786e-08</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.447677711041706e-08</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.733717169827287e-08</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.26750559942468e-09</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.644932723365855e-08</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.402607535145762e-08</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>9.364829800517782e-09</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>3.006065796284929e-08</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.606844956038913e-08</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>3.735450615494074e-09</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>9.414462098789045e-09</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>9.001362433203042e-10</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.348285749713796e-08</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.282854800166433e-08</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.560463047667326e-08</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.227281718589438e-09</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.851710310229464e-09</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.141964460771305e-07</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.975670180902171e-09</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.966042072534037e-08</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.880809249627418e-08</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>7.687117431487422e-08</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.830346185727194e-08</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.446421649120566e-08</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.819259296657719e-09</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>9.864552730221021e-09</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.268267244673552e-08</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>8.136788132162565e-09</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.523850556850448e-08</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.006014281936586e-08</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.328564529032519e-08</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.069133892528384e-09</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.960942519474429e-11</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>9.953638802073783e-09</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2.889403383221634e-08</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>4.651648310982637e-08</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>2.271594468084004e-08</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5.927052626475415e-09</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3.741801180012772e-08</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2.426716072534418e-08</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2.535090004585072e-08</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>3.239732482285262e-09</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>5.859036589228594e-10</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>8.780699722876761e-09</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>6.870331503705529e-08</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>5.024471505521433e-09</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>2.674988586193194e-08</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>3.208428012158038e-08</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>2.838004853344955e-08</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>5.105747824529772e-09</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>4.031110023561268e-08</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>1.422018680585779e-08</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>9.324424787848784e-09</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>3.182827157388601e-08</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>8.578015631144353e-09</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>1.711188346575909e-08</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>9.503120068643511e-09</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>2.168432544635834e-09</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>4.914392448540639e-09</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.083413359026508e-09</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1.553918549390687e-09</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>3.263323122837392e-08</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.839336860598451e-08</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>8.960144626257716e-09</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>6.321738510450814e-08</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>1.137246528060132e-07</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>4.605970360671563e-08</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>1.082158362919472e-09</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>3.260131009596989e-08</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.322784815016576e-08</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.27598642762905e-08</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>2.967036039080995e-08</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>8.771070980628792e-09</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.82726944078604e-08</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.187635412236432e-08</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>4.585108737131804e-09</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.113016967480007e-08</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.854740888125207e-10</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>6.089277970744433e-09</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>3.374065471462018e-08</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.126813842233787e-08</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>9.509476761593305e-09</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>1.634933077809819e-08</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>2.000344423436218e-08</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>4.681299792252958e-10</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>1.074673239287449e-08</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>2.930728193462073e-08</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>2.415988475945596e-08</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>3.61855700958813e-09</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>5.954568393917725e-09</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>7.524247891410596e-09</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>1.649678615933681e-08</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>2.368481410996992e-09</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>4.88900653294877e-09</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>2.623804462587032e-08</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>4.138207643222813e-08</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>1.433930840732955e-08</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>1.812877492568532e-08</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>1.259972304268331e-08</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>5.571542782689676e-09</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>1.471711996714475e-08</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>5.78444563359426e-08</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>5.739173047913937e-08</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>2.507896645909113e-08</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>4.951338894443325e-09</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>2.146268052172218e-08</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>1.5634663341757e-08</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>4.659280961050172e-08</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>2.272400756453408e-08</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>8.386194849663298e-09</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>4.03560100892264e-08</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>2.114633090855023e-08</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>4.758238691948691e-09</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>1.231836410653386e-08</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>1.228237778150287e-08</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>3.063751563558981e-08</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>3.464777975636935e-08</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>2.397252529817706e-08</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>3.776266055410815e-08</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>9.465055406110423e-10</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>2.090359352280302e-08</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>1.304545982350191e-08</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>9.678776891064444e-09</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>3.248085578277937e-09</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>7.908023569314082e-09</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>3.606199783234842e-08</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>6.837219679312057e-09</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>2.442447133432779e-08</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>1.539080685120098e-08</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>5.991160456630951e-09</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>1.879023159290227e-09</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>3.388840319473729e-10</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>1.059546339554629e-09</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>2.17082227749188e-08</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>1.597068965963899e-08</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>1.313668995805983e-08</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>2.299475987399546e-08</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>2.348090255566149e-08</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>9.591732741398573e-09</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>4.131041730914831e-09</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>4.089474359147971e-08</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>3.745024557133547e-08</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>1.083101111021278e-07</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>1.095357848868161e-08</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>1.366389934531753e-08</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>6.3652827009264e-08</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>1.638196245323797e-08</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>4.099626949027879e-08</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>4.464662417547061e-09</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>1.387207859693262e-08</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>1.22645884559347e-08</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>8.805516316101603e-09</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>1.368963964409886e-08</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>3.884760246819496e-08</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>7.191575335241396e-09</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>3.069727227966723e-08</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>2.430886603121962e-08</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>2.204558136043033e-08</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>5.97454796746888e-09</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>3.35112098071022e-08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.03945957124233246</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2585409879684448</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.07443378120660782</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1757493764162064</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.07615058124065399</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1581494063138962</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05436941981315613</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.04682494699954987</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.452660843729973e-05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.03072222694754601</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.266540914773941</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1156585440039635</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2468607872724533</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.02561983466148376</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1237173229455948</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.03446246311068535</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.000189618207514286</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.02174307219684124</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01726817339658737</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.01228365581482649</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.02253511175513268</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01814777962863445</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.01300882454961538</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.08106136322021484</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01031823083758354</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.007102535106241703</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.03514006361365318</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.03491082787513733</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.05430078506469727</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.01706202328205109</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.0578744113445282</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.05976145341992378</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.07985696196556091</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.02313409745693207</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.000718339579179883</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.01929246820509434</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.01021325215697289</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.05330278724431992</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.05157815665006638</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.07110780477523804</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.06040254235267639</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.06454211473464966</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.0263073742389679</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.00453562568873167</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.0226384736597538</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.01490694843232632</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.1371135115623474</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.02492091991007328</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.1143563538789749</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.04470592364668846</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.06542038917541504</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.006129861809313297</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.004880701191723347</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.04071449488401413</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.0005602422170341015</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.02671932056546211</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.04592444747686386</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.0175066702067852</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.06419380754232407</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.001887771068140864</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.01173514127731323</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.002294757403433323</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.03995890915393829</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.01068648137152195</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.01297865062952042</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.01681160554289818</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.007666071876883507</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.007395112421363592</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.0222394410520792</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.03334508091211319</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.02767330221831799</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.01967213675379753</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.02737441845238209</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.05628909170627594</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.03793760761618614</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.08211338520050049</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.02163631841540337</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.0898914709687233</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.007870232686400414</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.001422578934580088</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.02102208696305752</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.0004222539719194174</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.08328709006309509</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.02469798177480698</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.06816627085208893</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.02116210013628006</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.02250498533248901</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.00094635970890522</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.0222379844635725</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.001381058362312615</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.004244683310389519</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.03295706212520599</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.07742917537689209</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.09124310314655304</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.03005185350775719</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.02319724671542645</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.0301637090742588</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.03345498070120811</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.005262923426926136</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.008535638451576233</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.07815428823232651</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.02762938290834427</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.06979154050350189</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.007003399077802896</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.02568835020065308</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.001514012925326824</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.02315469644963741</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.005317671224474907</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.03976470232009888</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.04938842356204987</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.01616155356168747</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.03341434523463249</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.0472177267074585</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.09465824067592621</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.007749031763523817</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.136932373046875</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.02837926894426346</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.01251776516437531</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.04814709722995758</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.01381395943462849</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.03116980940103531</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.02302936837077141</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.0293608270585537</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.01187929697334766</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.02991389855742455</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.07998938113451004</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.03001283295452595</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.01482641138136387</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.05316329002380371</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.02117940410971642</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.05172114074230194</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.04378486052155495</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.0007878390606492758</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.1045530363917351</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.0676429271697998</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.01002433523535728</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.07398894429206848</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.008911481127142906</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.05947351083159447</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.006279652006924152</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.01775402948260307</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.00416117999702692</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.009753688238561153</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.006943793501704931</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.01182607747614384</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.04394196718931198</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.01801920309662819</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.05707566440105438</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.0138665959239006</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.04841352254152298</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.03731326386332512</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.03059178218245506</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.05290559306740761</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.00598751800134778</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.09181177616119385</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.02559324353933334</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.07773339003324509</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.01942427083849907</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.03898539394140244</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.004041638225317001</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.03337621316313744</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.006170430686324835</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.01475078053772449</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.03400800377130508</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.01189100276678801</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.05871568992733955</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.06404419988393784</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.04125352203845978</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.02508959546685219</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.004569119773805141</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.01489393040537834</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.02110689878463745</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.08051186054944992</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.03180558234453201</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.003383874893188477</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.02970932424068451</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.02761543542146683</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.007661303505301476</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.001438160426914692</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.07564431428909302</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.006602088455110788</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.03711588308215141</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.03089665621519089</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.02427799813449383</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.03217052295804024</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.03650979325175285</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.0521286241710186</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.04178095236420631</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.00729341572150588</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.2477831840515137</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.249485731124878</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1823394745588303</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3340487480163574</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.497701108455658</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9710496664047241</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4138206243515015</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.373165249824524</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2934057116508484</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1220884323120117</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.437557220458984</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4040325284004211</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.6904899477958679</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.561481356620789</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.140895366668701</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2955837249755859</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.132053971290588</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4773496389389038</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2653692960739136</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.2745325267314911</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1066605970263481</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5303171873092651</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3336752951145172</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.2069061994552612</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1213735491037369</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.146401658654213</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.03736450523138046</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.1460432261228561</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.4099324643611908</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.05804060772061348</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.5456782579421997</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.4052363038063049</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.2613713145256042</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.09303116053342819</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.4194482266902924</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.2477362751960754</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.3739300072193146</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.4508432745933533</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.09954799711704254</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.07126937806606293</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.2426281124353409</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.2663604319095612</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.1260051876306534</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.2424988597631454</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.07023195922374725</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.17624731361866</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.31489896774292</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.009530603885650635</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.3299360573291779</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.2526752650737762</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.8199564814567566</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.1102865785360336</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.3549195528030396</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.1522448658943176</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.0914057120680809</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.8179105520248413</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.1401531547307968</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.2287320047616959</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.3716838657855988</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.1304492503404617</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.08836867660284042</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.6239086389541626</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.08784027397632599</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.06485982239246368</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.2523485124111176</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.4608637690544128</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.1880350410938263</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.254668653011322</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.1907695680856705</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.4615427851676941</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.02104010619223118</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.02819657325744629</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.2521125674247742</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.9246677160263062</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.08467274904251099</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.427854984998703</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.421746551990509</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.4621808230876923</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.3797600269317627</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.2959935367107391</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.009715599939227104</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.09532581269741058</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.4171262979507446</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.1479971706867218</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.08887046575546265</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.2241176217794418</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.2567138373851776</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.09192316234111786</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.07292833179235458</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.001374331535771489</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.3980901539325714</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.4701363444328308</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.27647864818573</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.8198738098144531</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.4906374514102936</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.231806144118309</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.01302499324083328</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.1976212859153748</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.009439745917916298</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.1914399862289429</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.3750704824924469</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.1594295054674149</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.1593695878982544</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.2258796393871307</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.3375994265079498</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.004770191386342049</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.05061706900596619</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.001547748222947121</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.002765856683254242</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.1834245920181274</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.09887558221817017</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.2094705551862717</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.5938735604286194</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.4955756664276123</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.09896544367074966</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.07015302777290344</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.07450702041387558</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.2342185080051422</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.1575074791908264</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.09800518304109573</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.09501535445451736</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.3414133489131927</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.1586684435606003</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.1980219781398773</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.109615758061409</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.4388586282730103</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.2186708450317383</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.4610362946987152</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0.1943665593862534</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.05545004457235336</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.2014835476875305</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.04032621160149574</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.01022737473249435</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.3354416191577911</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.4020067155361176</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.02088253758847713</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.2866785526275635</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.1827481240034103</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.08620554208755493</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.3113581538200378</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.1308719962835312</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.03412406146526337</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.1342763602733612</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.02087635919451714</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.2163719087839127</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.2987370491027832</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.1777446866035461</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.0324598103761673</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.1731580495834351</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.3293160498142242</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.03038715943694115</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.06518743932247162</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.2804095447063446</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.1515016108751297</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.4695470333099365</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.1075715124607086</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.1941046714782715</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.1695429086685181</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.3240395188331604</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.1224187165498734</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0.07233456522226334</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.03587856888771057</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.06182720139622688</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1569430083036423</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.2669805884361267</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.2730588614940643</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.01282184571027756</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.2338248640298843</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.3508687317371368</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.1715506911277771</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.4770954251289368</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.2411908209323883</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.05156783759593964</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.2506526112556458</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.398493617773056</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.7233131527900696</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0.1404696702957153</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.2001593112945557</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.5632615089416504</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.3846611976623535</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.1039706170558929</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.007475625723600388</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.2922214865684509</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.1217491328716278</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.2757357656955719</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.05836183577775955</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.2628820538520813</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.08427408337593079</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.07140614092350006</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.0173579528927803</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.143392950296402</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.03967835009098053</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.07939842343330383</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.03553188592195511</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.06773848086595535</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.03688123449683189</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.02881435118615627</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.002065684180706739</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.005785331595689058</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1513591557741165</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0620359480381012</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1033966690301895</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.001202106475830078</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05984050780534744</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.03201362863183022</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.006249841302633286</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.001826814608648419</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.005330659449100494</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.001719023333862424</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.001835565082728863</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.006764289923012257</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.01111030578613281</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.01457347627729177</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.01289683021605015</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.01274039130657911</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.01537073589861393</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.009097556583583355</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.01315546501427889</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.02140726149082184</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.02858113311231136</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.002171211410313845</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.02850360237061977</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.005829052533954382</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.02953095361590385</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.0006703162216581404</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.002231928054243326</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.03557135164737701</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.01189426332712173</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.02519211731851101</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.0246244054287672</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.009549652226269245</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.0001127682626247406</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.004675420466810465</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.007454728707671165</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.001433736528269947</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.09365704655647278</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.005882579367607832</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.04447688162326813</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.05516980960965157</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.03322672471404076</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.0016557602211833</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.007688106968998909</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.01734555512666702</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.009246683679521084</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.008135367184877396</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.0355362594127655</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.004082370083779097</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.04925133660435677</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.002083261497318745</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.0156575795263052</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.01305107120424509</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.005875005386769772</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.0005514742806553841</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.009978123009204865</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.0009111935505643487</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.0003682449460029602</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.00665539363399148</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.002588521922007203</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.008889723569154739</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.004822059068828821</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.002287278650328517</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.004157275892794132</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.04722563177347183</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.007541458588093519</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0.03411151841282845</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.02542989701032639</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.02970365062355995</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.01807856373488903</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.002700039651244879</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.009002177976071835</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.001107400166802108</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.05034935474395752</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.009832674637436867</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.02520578354597092</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.008732794784009457</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.01147282402962446</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.0007405718788504601</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.006649925373494625</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.0006787808961234987</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.01456786505877972</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0.03389590233564377</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.03082234784960747</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.03519664704799652</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.02787601202726364</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.01411617826670408</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.008501132018864155</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0.007738359272480011</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.006688691210001707</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.003651150967925787</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.04695425182580948</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0.01163076423108578</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.02790304645895958</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.004267758224159479</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.01401581615209579</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0.002028207760304213</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0.006914286874234676</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0.001889131381176412</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.01034097746014595</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0.04116978868842125</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.01926041953265667</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.02545507997274399</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.01124199572950602</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.05983690917491913</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0.004853304475545883</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.03899464011192322</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0.01889238506555557</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.00301754311658442</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0.02642524614930153</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0.002851246390491724</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.01179956831037998</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.003228401532396674</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.008770524524152279</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.01943063735961914</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0.01386185642331839</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0.02744186297059059</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.008265157230198383</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.01336892601102591</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0.02570491470396519</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.008265722543001175</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.0336768701672554</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.01541204936802387</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>8.403474930673838e-05</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0.04392808675765991</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0.03732273727655411</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0.006036865524947643</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0.0389418751001358</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0.008320675231516361</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.01563384383916855</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.009410591796040535</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.01190703734755516</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0.005736632738262415</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0.001589602325111628</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0.000229745201067999</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0.007032059133052826</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.0372910350561142</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0.006489268038421869</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.0216006264090538</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.015026630833745</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.007798645179718733</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0.01178634166717529</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0.01344534289091825</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0.01524746604263783</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0.002391489455476403</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0.0531998872756958</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0.009605655446648598</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.02912761270999908</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.007855480536818504</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.01639106497168541</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0.001519514131359756</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0.01069539040327072</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0.00389961781911552</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0.005920895840972662</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.01414401456713676</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0.003396585583686829</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.01424596086144447</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.02391773462295532</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.01517410110682249</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0.005850042216479778</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0.0003806446329690516</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0.005999875254929066</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0.00938178226351738</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.03668200224637985</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0.02823209762573242</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.0002023251727223396</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.01115156151354313</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0.01365816127508879</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0.009315176866948605</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0.003405659925192595</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0.04585897177457809</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0.009105545468628407</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0.01498557161539793</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0.01217467151582241</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.0188300684094429</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0.001878047944046557</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.01324799377471209</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0.02893620729446411</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0.007197771221399307</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0.002072129398584366</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
